--- a/files/Automated Multi-Year Financial Projection Model.xlsx
+++ b/files/Automated Multi-Year Financial Projection Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suleman/Documents/AIr University/7th Semester/Financial modeling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suleman/Documents/my-portfolio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5AF19F-911C-DF44-B3EC-9DC907E82276}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA7DAF3-9D2E-C94C-B070-C034B5CE252C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showSheetTabs="0" xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16080" xr2:uid="{F97DBC22-3B42-654B-8BF3-BF1CD6013AE4}"/>
   </bookViews>
@@ -1692,11 +1692,8 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Suleman Arshad      220746
-Aimen Shabir            220804
-Duaa Faisal                 220802
-Ubaid ur Rehman     220810
-Iraj Shaukat               220760</t>
+    <t xml:space="preserve">Suleman Arshad  
+</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1703,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1842,12 +1839,6 @@
       <sz val="20"/>
       <color theme="0"/>
       <name val="Arial Rounded MT Bold"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="22"/>
-      <color theme="0"/>
-      <name val="Gill Sans Ultra Bold"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2327,7 +2318,7 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="31"/>
     </xf>
   </cellXfs>
